--- a/excel/output_stats_vfvv/adi/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/adi/PerSubgraphStats.xlsx
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>63</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>58</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
         <v>42</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K10" t="n">
         <v>97</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1001500</v>
+        <v>1750750</v>
       </c>
       <c r="K12" t="n">
         <v>8245240</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>13</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
         <v>20</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>77</v>
